--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2020_T4_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2020_T4_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>76</t>
+    <t>70</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,40 +57,40 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.368</t>
-  </si>
-  <si>
-    <t>(0.056)</t>
-  </si>
-  <si>
-    <t>0.513</t>
-  </si>
-  <si>
-    <t>(0.058)</t>
-  </si>
-  <si>
-    <t>0.276</t>
-  </si>
-  <si>
-    <t>(0.052)</t>
-  </si>
-  <si>
-    <t>1.408</t>
-  </si>
-  <si>
-    <t>(0.460)</t>
-  </si>
-  <si>
-    <t>1.329</t>
-  </si>
-  <si>
-    <t>(0.215)</t>
-  </si>
-  <si>
-    <t>0.447</t>
-  </si>
-  <si>
-    <t>(0.103)</t>
+    <t>0.400</t>
+  </si>
+  <si>
+    <t>(0.059)</t>
+  </si>
+  <si>
+    <t>0.557</t>
+  </si>
+  <si>
+    <t>(0.060)</t>
+  </si>
+  <si>
+    <t>0.300</t>
+  </si>
+  <si>
+    <t>(0.055)</t>
+  </si>
+  <si>
+    <t>1.529</t>
+  </si>
+  <si>
+    <t>(0.497)</t>
+  </si>
+  <si>
+    <t>1.443</t>
+  </si>
+  <si>
+    <t>(0.228)</t>
+  </si>
+  <si>
+    <t>0.486</t>
+  </si>
+  <si>
+    <t>(0.111)</t>
   </si>
   <si>
     <t>40</t>
@@ -138,7 +138,7 @@
     <t>(0.290)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -150,22 +150,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.132</t>
-  </si>
-  <si>
-    <t>0.337***</t>
-  </si>
-  <si>
-    <t>0.399***</t>
-  </si>
-  <si>
-    <t>0.892</t>
-  </si>
-  <si>
-    <t>2.621***</t>
-  </si>
-  <si>
-    <t>1.153***</t>
+    <t>0.100</t>
+  </si>
+  <si>
+    <t>0.293***</t>
+  </si>
+  <si>
+    <t>0.375***</t>
+  </si>
+  <si>
+    <t>0.771</t>
+  </si>
+  <si>
+    <t>2.507***</t>
+  </si>
+  <si>
+    <t>1.114***</t>
   </si>
 </sst>
 </file>
